--- a/degital_value_list.xlsx
+++ b/degital_value_list.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project\ZCS_DegitalValueList\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D757C318-5B15-4CA1-B7E7-7331B9803676}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E4ED906-8F27-4DE5-B8D3-E89BF87249D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7425" yWindow="3000" windowWidth="16860" windowHeight="10065" xr2:uid="{8DBE219E-1175-4BAE-AFFC-8F7B76384628}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{8DBE219E-1175-4BAE-AFFC-8F7B76384628}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,10 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
-  <si>
-    <t>【未承認版】</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>№</t>
   </si>
@@ -65,24 +62,24 @@
     <t>発送単位</t>
   </si>
   <si>
-    <t>【{yyyy.mm}～】
+    <t>改定額</t>
+  </si>
+  <si>
+    <t>送料</t>
+  </si>
+  <si>
+    <t>備考</t>
+  </si>
+  <si>
+    <t>改定理由</t>
+  </si>
+  <si>
+    <t>【2025.11～】
 県連価格</t>
   </si>
   <si>
-    <t>改定額</t>
-  </si>
-  <si>
-    <t>【{yyyy.mm}】
+    <t>【2025.11】
 参考小売価格</t>
-  </si>
-  <si>
-    <t>送料</t>
-  </si>
-  <si>
-    <t>備考</t>
-  </si>
-  <si>
-    <t>改定理由</t>
   </si>
 </sst>
 </file>
@@ -343,13 +340,13 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="38" fontId="5" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="38" fontId="5" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="38" fontId="5" fillId="2" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="38" fontId="5" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="38" fontId="5" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="38" fontId="5" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -361,16 +358,16 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="38" fontId="8" fillId="5" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="38" fontId="8" fillId="5" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="38" fontId="8" fillId="4" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="38" fontId="8" fillId="4" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="38" fontId="8" fillId="4" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="38" fontId="8" fillId="4" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="38" fontId="8" fillId="4" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="38" fontId="8" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -711,24 +708,22 @@
   <dimension ref="A1:N4"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="30.875" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="10.875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.75" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.25" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="44.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.25" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="39.625" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="10.875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="27.125" customWidth="1"/>
+    <col min="5" max="5" width="69.75" customWidth="1"/>
+    <col min="6" max="6" width="27.125" customWidth="1"/>
+    <col min="7" max="7" width="42" customWidth="1"/>
+    <col min="8" max="8" width="27.125" customWidth="1"/>
+    <col min="9" max="9" width="40.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="34.75" customWidth="1"/>
+    <col min="11" max="11" width="35.625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="29.375" customWidth="1"/>
+    <col min="13" max="13" width="67.75" customWidth="1"/>
+    <col min="14" max="14" width="56.375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" s="5" customFormat="1" ht="42.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="A1" s="1"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -760,46 +755,46 @@
     </row>
     <row r="3" spans="1:14" s="11" customFormat="1" ht="99.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="C3" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="D3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="E3" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="F3" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="G3" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="15" t="s">
+      <c r="H3" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="13" t="s">
+      <c r="I3" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="J3" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="16" t="s">
+      <c r="K3" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="L3" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="J3" s="17" t="s">
+      <c r="M3" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="16" t="s">
+      <c r="N3" s="18" t="s">
         <v>11</v>
-      </c>
-      <c r="L3" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="M3" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="N3" s="18" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:14" s="11" customFormat="1" ht="99.95" customHeight="1" x14ac:dyDescent="0.4">
